--- a/budget-database.xlsx
+++ b/budget-database.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Transactions" sheetId="2" r:id="rId2"/>
+    <sheet name="Expense History" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -417,7 +418,7 @@
         <v>Total income</v>
       </c>
       <c r="B2">
-        <v>3650</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -425,7 +426,7 @@
         <v>Total expenses</v>
       </c>
       <c r="B3">
-        <v>1278.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -433,7 +434,7 @@
         <v>Available balance</v>
       </c>
       <c r="B4">
-        <v>2371.55</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -445,7 +446,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G20"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -463,121 +482,461 @@
         <v>Date</v>
       </c>
       <c r="C1" t="str">
+        <v>HistoryTitle</v>
+      </c>
+      <c r="D1" t="str">
         <v>Description</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Category</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Type</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Amount</v>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>1</v>
+        <v>1790137963296</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-17</v>
       </c>
       <c r="C2" t="str">
-        <v>Monthly salary</v>
+        <v>sept</v>
       </c>
       <c r="D2" t="str">
-        <v>Salary</v>
+        <v>basta</v>
       </c>
       <c r="E2" t="str">
-        <v>income</v>
-      </c>
-      <c r="F2">
-        <v>3200</v>
+        <v>Other</v>
+      </c>
+      <c r="F2" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G2">
+        <v>650</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>2</v>
+        <v>1790137946168</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-18</v>
       </c>
       <c r="C3" t="str">
-        <v>Apartment rent</v>
+        <v>sept</v>
       </c>
       <c r="D3" t="str">
-        <v>Housing</v>
+        <v>ewan</v>
       </c>
       <c r="E3" t="str">
-        <v>expense</v>
-      </c>
-      <c r="F3">
-        <v>1150</v>
+        <v>Other</v>
+      </c>
+      <c r="F3" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G3">
+        <v>1250</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>3</v>
+        <v>1790137914840</v>
       </c>
       <c r="B4" t="str">
         <v>2026-09-19</v>
       </c>
       <c r="C4" t="str">
-        <v>Grocery run</v>
+        <v>sept</v>
       </c>
       <c r="D4" t="str">
-        <v>Food</v>
+        <v>internet</v>
       </c>
       <c r="E4" t="str">
-        <v>expense</v>
-      </c>
-      <c r="F4">
-        <v>86.45</v>
+        <v>Other</v>
+      </c>
+      <c r="F4" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G4">
+        <v>1500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>4</v>
+        <v>1790137897760</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-19</v>
       </c>
       <c r="C5" t="str">
-        <v>Freelance project</v>
+        <v>sept</v>
       </c>
       <c r="D5" t="str">
-        <v>Side income</v>
+        <v>egg</v>
       </c>
       <c r="E5" t="str">
-        <v>income</v>
-      </c>
-      <c r="F5">
-        <v>450</v>
+        <v>Food</v>
+      </c>
+      <c r="F5" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G5">
+        <v>460</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
+        <v>1790137874096</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-09-20</v>
+      </c>
+      <c r="C6" t="str">
+        <v>sept</v>
+      </c>
+      <c r="D6" t="str">
+        <v>gala sa mall</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Shopping</v>
+      </c>
+      <c r="F6" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G6">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>1790137597376</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-09-21</v>
+      </c>
+      <c r="C7" t="str">
+        <v>sept</v>
+      </c>
+      <c r="D7" t="str">
+        <v>tinapay</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F7" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>1790137578496</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-09-22</v>
+      </c>
+      <c r="C8" t="str">
+        <v>sept</v>
+      </c>
+      <c r="D8" t="str">
+        <v>ulam</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F8" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>1790137551993</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="C9" t="str">
+        <v>sept</v>
+      </c>
+      <c r="D9" t="str">
+        <v>rice</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F9" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>2026-09-18</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Train pass</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Transport</v>
-      </c>
-      <c r="E6" t="str">
-        <v>expense</v>
-      </c>
-      <c r="F6">
-        <v>42</v>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>1790141129019</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="C10" t="str">
+        <v>sept</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Total income</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Summary</v>
+      </c>
+      <c r="F10" t="str">
+        <v>income</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>1790141129020</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="C11" t="str">
+        <v>sept</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Total expenses</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Summary</v>
+      </c>
+      <c r="F11" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G11">
+        <v>6475</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>1790141229743</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="C12" t="str">
+        <v>sept30</v>
+      </c>
+      <c r="D12" t="str">
+        <v>fdgfdg</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F12" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G12">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>1790141220327</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C13" t="str">
+        <v>sept30</v>
+      </c>
+      <c r="D13" t="str">
+        <v>mnjf</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F13" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G13">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>1790141208199</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-09-13</v>
+      </c>
+      <c r="C14" t="str">
+        <v>sept30</v>
+      </c>
+      <c r="D14" t="str">
+        <v>dfssd</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F14" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G14">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>1790141197870</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-09-12</v>
+      </c>
+      <c r="C15" t="str">
+        <v>sept30</v>
+      </c>
+      <c r="D15" t="str">
+        <v>fsdfds</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F15" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G15">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>1790141187839</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-09-11</v>
+      </c>
+      <c r="C16" t="str">
+        <v>sept30</v>
+      </c>
+      <c r="D16" t="str">
+        <v>dgdff</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F16" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G16">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>1790141172143</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="C17" t="str">
+        <v>sept30</v>
+      </c>
+      <c r="D17" t="str">
+        <v>sdfasdsa</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F17" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G17">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>1790141159279</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="C18" t="str">
+        <v>sept30</v>
+      </c>
+      <c r="D18" t="str">
+        <v>sadsa</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Food</v>
+      </c>
+      <c r="F18" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G18">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>1790141239752</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="C19" t="str">
+        <v>sept30</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Total income</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Summary</v>
+      </c>
+      <c r="F19" t="str">
+        <v>income</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>1790141239753</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="C20" t="str">
+        <v>sept30</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Total expenses</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Summary</v>
+      </c>
+      <c r="F20" t="str">
+        <v>expense</v>
+      </c>
+      <c r="G20">
+        <v>5133</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/budget-database.xlsx
+++ b/budget-database.xlsx
@@ -418,7 +418,7 @@
         <v>Total income</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="3">
@@ -426,7 +426,7 @@
         <v>Total expenses</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>4685</v>
       </c>
     </row>
     <row r="4">
@@ -434,7 +434,7 @@
         <v>Available balance</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -446,7 +446,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F11"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -455,9 +455,230 @@
     <col min="5" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Amount</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1790321283718</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="C2" t="str">
+        <v>meralco</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E2" t="str">
+        <v>expense</v>
+      </c>
+      <c r="F2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1790321114942</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C3" t="str">
+        <v>tubig</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E3" t="str">
+        <v>expense</v>
+      </c>
+      <c r="F3">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1790320999045</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="C4" t="str">
+        <v>kfc tubo savings</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E4" t="str">
+        <v>expense</v>
+      </c>
+      <c r="F4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>1790320971453</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-09-13</v>
+      </c>
+      <c r="C5" t="str">
+        <v>tinapay</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Food</v>
+      </c>
+      <c r="E5" t="str">
+        <v>expense</v>
+      </c>
+      <c r="F5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>1790320961677</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-09-13</v>
+      </c>
+      <c r="C6" t="str">
+        <v>fries</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Food</v>
+      </c>
+      <c r="E6" t="str">
+        <v>expense</v>
+      </c>
+      <c r="F6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>1790320929405</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-09-12</v>
+      </c>
+      <c r="C7" t="str">
+        <v>fast food</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Food</v>
+      </c>
+      <c r="E7" t="str">
+        <v>expense</v>
+      </c>
+      <c r="F7">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>1790320918557</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-09-12</v>
+      </c>
+      <c r="C8" t="str">
+        <v>cofee</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Food</v>
+      </c>
+      <c r="E8" t="str">
+        <v>expense</v>
+      </c>
+      <c r="F8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>1790320883397</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-09-11</v>
+      </c>
+      <c r="C9" t="str">
+        <v>centro mall</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Transport</v>
+      </c>
+      <c r="E9" t="str">
+        <v>expense</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>1790320870341</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-09-11</v>
+      </c>
+      <c r="C10" t="str">
+        <v>bigas</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Food</v>
+      </c>
+      <c r="E10" t="str">
+        <v>expense</v>
+      </c>
+      <c r="F10">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>1790320849949</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-09-11</v>
+      </c>
+      <c r="C11" t="str">
+        <v>from Aine</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E11" t="str">
+        <v>income</v>
+      </c>
+      <c r="F11">
+        <v>5000</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/budget-database.xlsx
+++ b/budget-database.xlsx
@@ -426,7 +426,7 @@
         <v>Total expenses</v>
       </c>
       <c r="B3">
-        <v>4685</v>
+        <v>4115</v>
       </c>
     </row>
     <row r="4">
@@ -434,7 +434,7 @@
         <v>Available balance</v>
       </c>
       <c r="B4">
-        <v>315</v>
+        <v>885</v>
       </c>
     </row>
   </sheetData>
@@ -446,7 +446,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -578,13 +578,13 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1790320929405</v>
+        <v>1790320918557</v>
       </c>
       <c r="B7" t="str">
         <v>2026-09-12</v>
       </c>
       <c r="C7" t="str">
-        <v>fast food</v>
+        <v>cofee</v>
       </c>
       <c r="D7" t="str">
         <v>Food</v>
@@ -593,92 +593,52 @@
         <v>expense</v>
       </c>
       <c r="F7">
-        <v>320</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>1790320918557</v>
+        <v>1790320883397</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-09-12</v>
+        <v>2026-09-11</v>
       </c>
       <c r="C8" t="str">
-        <v>cofee</v>
+        <v>centro mall</v>
       </c>
       <c r="D8" t="str">
-        <v>Food</v>
+        <v>Transport</v>
       </c>
       <c r="E8" t="str">
         <v>expense</v>
       </c>
       <c r="F8">
-        <v>200</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>1790320883397</v>
+        <v>1790320849949</v>
       </c>
       <c r="B9" t="str">
         <v>2026-09-11</v>
       </c>
       <c r="C9" t="str">
-        <v>centro mall</v>
+        <v>from Aine</v>
       </c>
       <c r="D9" t="str">
-        <v>Transport</v>
+        <v>Salary</v>
       </c>
       <c r="E9" t="str">
-        <v>expense</v>
+        <v>income</v>
       </c>
       <c r="F9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>1790320870341</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-09-11</v>
-      </c>
-      <c r="C10" t="str">
-        <v>bigas</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Food</v>
-      </c>
-      <c r="E10" t="str">
-        <v>expense</v>
-      </c>
-      <c r="F10">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>1790320849949</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-09-11</v>
-      </c>
-      <c r="C11" t="str">
-        <v>from Aine</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Salary</v>
-      </c>
-      <c r="E11" t="str">
-        <v>income</v>
-      </c>
-      <c r="F11">
         <v>5000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
   </ignoredErrors>
 </worksheet>
 </file>
